--- a/AAII_Financials/Yearly/TAK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TAK_YR_FIN.xlsx
@@ -656,186 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>28337000</v>
+      </c>
+      <c r="E8" s="3">
         <v>30595100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28189200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>30296800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>29390500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28913600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30586700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18926300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16670900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11674000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10183400</v>
+      </c>
+      <c r="E9" s="3">
         <v>10493800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9464200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9427000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9283300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9165100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10410100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5881200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4666000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3766000</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18153600</v>
+      </c>
+      <c r="E10" s="3">
         <v>20101300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>18725000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20869900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20107200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19748400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20176600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13045100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12004800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7908000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,47 +863,51 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4204700</v>
+      </c>
+      <c r="E12" s="3">
         <v>4876400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4817100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4764200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4332300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4120900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4573200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3323300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3064300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2104900</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,87 +944,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3835200</v>
+      </c>
+      <c r="E14" s="3">
         <v>1664700</v>
       </c>
-      <c r="E14" s="3">
-        <v>2011600</v>
-      </c>
       <c r="F14" s="3">
+        <v>2027600</v>
+      </c>
+      <c r="G14" s="3">
         <v>895200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1107000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-770500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1834800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-11900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-804800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>243600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3150200</v>
+      </c>
+      <c r="E15" s="3">
         <v>3660700</v>
       </c>
-      <c r="E15" s="3">
-        <v>3448000</v>
-      </c>
       <c r="F15" s="3">
+        <v>3427300</v>
+      </c>
+      <c r="G15" s="3">
         <v>3649200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3448700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3663900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3785600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1533400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1186600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1056300</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1021,86 +1046,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24514200</v>
+      </c>
+      <c r="E17" s="3">
         <v>26835900</v>
       </c>
-      <c r="E17" s="3">
-        <v>24887000</v>
-      </c>
       <c r="F17" s="3">
+        <v>24866400</v>
+      </c>
+      <c r="G17" s="3">
         <v>25635400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24449000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25079500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27829500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16972300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14996500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10623500</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3822800</v>
+      </c>
+      <c r="E18" s="3">
         <v>3759200</v>
       </c>
-      <c r="E18" s="3">
-        <v>3302200</v>
-      </c>
       <c r="F18" s="3">
+        <v>3322900</v>
+      </c>
+      <c r="G18" s="3">
         <v>4661500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4941500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3834100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2757200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1954000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1674400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1050500</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1116,203 +1148,219 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E20" s="3">
         <v>187400</v>
       </c>
-      <c r="E20" s="3">
-        <v>255600</v>
-      </c>
       <c r="F20" s="3">
+        <v>260200</v>
+      </c>
+      <c r="G20" s="3">
         <v>108200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>373800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>130000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>219700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>463000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-33400</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6913400</v>
+      </c>
+      <c r="E21" s="3">
         <v>7232500</v>
       </c>
-      <c r="E21" s="3">
-        <v>6494600</v>
-      </c>
       <c r="F21" s="3">
+        <v>6490000</v>
+      </c>
+      <c r="G21" s="3">
         <v>8202500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8016400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7368000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6323200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3024500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2460700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2177700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>931600</v>
+      </c>
+      <c r="E22" s="3">
         <v>871400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>762900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>879900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1008200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1182700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1384800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>434600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>94500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>51000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-895300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1169200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>349000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2821600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2491600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3311400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-564600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1151600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2045100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>966200</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E24" s="3">
         <v>447000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-604300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>436700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>596200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-89800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-976200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-67400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>287200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>187600</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1349,87 +1397,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-956700</v>
+      </c>
+      <c r="E26" s="3">
         <v>722200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>953300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2384900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1895400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3401200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>411600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1219000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1758000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>778600</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-958400</v>
+      </c>
+      <c r="E27" s="3">
         <v>720700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>952500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2384800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1894500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3399700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>411100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1220000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1759700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>774700</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1466,9 +1523,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1505,9 +1565,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1544,9 +1607,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1583,87 +1649,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-59600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-187400</v>
       </c>
-      <c r="E32" s="3">
-        <v>-255600</v>
-      </c>
       <c r="F32" s="3">
+        <v>-260200</v>
+      </c>
+      <c r="G32" s="3">
         <v>-108200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-373800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-130000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-219700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-463000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>33400</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-958400</v>
+      </c>
+      <c r="E33" s="3">
         <v>720700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>952500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2384800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1894500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3399700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>411200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1220000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1759700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>774700</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1700,92 +1775,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-958400</v>
+      </c>
+      <c r="E35" s="3">
         <v>720700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>952500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2384800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1894500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3399700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>411200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1220000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1759700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>774700</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1801,8 +1885,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1818,47 +1903,51 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3742400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2571700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3026700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4013500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6997200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8736300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5925700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6336000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2773100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1877000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1884,293 +1973,317 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>759300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>658200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5511400</v>
+      </c>
+      <c r="E43" s="3">
         <v>4843200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4612100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5128100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5965200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7348300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7294700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6760400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4037400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2997800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8783500</v>
+      </c>
+      <c r="E44" s="3">
         <v>8129300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7998900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7420700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7025800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6816300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7059300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8299500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2005000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1523600</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1399200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1292000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1278000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1476500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1370300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1628200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2670000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5614600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>582900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1438700</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19436500</v>
+      </c>
+      <c r="E46" s="3">
         <v>16836200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16915700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18038700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21358400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24529100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22949700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27010500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10157800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8495200</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E47" s="3">
         <v>72100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>593900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>746000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>795300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1016900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>997500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>976300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2866000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2042500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13336900</v>
+      </c>
+      <c r="E48" s="3">
         <v>13143500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13155100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12722300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13034200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13145800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12884200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12020000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5054400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3618300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>58038200</v>
+      </c>
+      <c r="E49" s="3">
         <v>59807100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>64029300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>68157000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>67742900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>71818200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>76057000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>81142700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19241200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14036800</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2207,9 +2320,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2246,48 +2362,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3251200</v>
+      </c>
+      <c r="E52" s="3">
         <v>2814100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2591600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2580300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2603600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3040000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3401100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2519700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>734200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1168500</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2324,48 +2446,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>97553600</v>
+      </c>
+      <c r="E54" s="3">
         <v>95148800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>99889500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>104997600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>108520000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>116748700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119152900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>124472300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38665400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29297400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2381,8 +2509,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2398,242 +2527,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2040000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2059800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2115300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2312800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2437000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2098600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1966800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1916300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1258900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>847300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3632600</v>
+      </c>
+      <c r="E58" s="3">
         <v>4096100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2865700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3003200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2123500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>654100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5835400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8908000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3673500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12138600</v>
+      </c>
+      <c r="E59" s="3">
         <v>10582400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10311700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13354500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13109400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13279800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12419600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12215600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5665100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4688400</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17811200</v>
+      </c>
+      <c r="E60" s="3">
         <v>16738300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15292700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18670500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17669900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16032500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20221700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23039900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6944200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9209200</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30808800</v>
+      </c>
+      <c r="E61" s="3">
         <v>29884900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33254600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33569100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37491800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45203300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>44932800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>44610300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9761000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4043100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1129100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1068800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1547700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1959300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1635700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2358000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2008200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2098100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1285700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2909100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2670,9 +2818,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2709,9 +2860,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2748,48 +2902,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>50821400</v>
+      </c>
+      <c r="E66" s="3">
         <v>48831100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>51798500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57194400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>61716600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69938400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75218000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>77671500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19670000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16530100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2805,8 +2965,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2843,9 +3004,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2882,9 +3046,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2921,9 +3088,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2960,48 +3130,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4480200</v>
+      </c>
+      <c r="E72" s="3">
         <v>7930600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9197700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11593300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12185400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13652100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12731800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14397900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14663200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10189600</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3038,9 +3214,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3077,9 +3256,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3116,48 +3298,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>46724600</v>
+      </c>
+      <c r="E76" s="3">
         <v>46311700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>48086100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>47799100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>46799200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46772900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43897700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46764600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18807300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12767300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3194,92 +3382,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-958400</v>
+      </c>
+      <c r="E81" s="3">
         <v>720700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>952500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2384800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1894500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3399700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>411200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1220000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1759700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>774700</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3295,47 +3492,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1094400</v>
+      </c>
+      <c r="E83" s="3">
         <v>1150000</v>
       </c>
-      <c r="E83" s="3">
-        <v>1146000</v>
-      </c>
       <c r="F83" s="3">
+        <v>4813100</v>
+      </c>
+      <c r="G83" s="3">
         <v>4998000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4802200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5060400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5424100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2235300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1714900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1155400</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3372,9 +3573,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3411,9 +3615,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3450,9 +3657,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3489,9 +3699,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3528,48 +3741,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6549700</v>
+      </c>
+      <c r="E89" s="3">
         <v>7059700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4736000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7350700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9248700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9140500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6224300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2964300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3557800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1614700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3585,47 +3804,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1106900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1340900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1159800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1058100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1015000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1005500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1181000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-701000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-630900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-415600</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3662,9 +3885,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3701,48 +3927,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2321600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2451200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3066800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4566900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1631500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3558200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2714800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25590600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-878900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4419400</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3758,47 +3990,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1961600</v>
+      </c>
+      <c r="E96" s="3">
         <v>2020000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1898700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2101900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2336000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2562000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2626200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1290100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1336000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-955000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3835,9 +4071,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3874,9 +4113,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3913,124 +4155,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3124600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5017900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2343200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5334600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8813600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9840500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9342000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>26588200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3071700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1953900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-76000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>173200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>172500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>236800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>113000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-202300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-282200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-43000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-38700</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1320300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-485400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2378400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-959600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2971200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-605100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3679700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-435800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-889500</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
